--- a/docs/最新版/02_管理シート/撮影案件管理_ヒアリングシート.xlsx
+++ b/docs/最新版/02_管理シート/撮影案件管理_ヒアリングシート.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,10 +49,16 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00E8740C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Menlo"/>
+      <color rgb="001E40AF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -110,9 +121,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,30 +494,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ぺいほーむ 撮影案件管理</t>
@@ -513,11 +527,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>撮影依頼〜撮影〜納品〜掲載までの全工程を一元管理するシート</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>撮影依頼〜撮影〜納品〜掲載までの全工程を一元管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -530,80 +544,79 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>掲載先
+(動画/事例/両方)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>工務店名</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>担当者名</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>連絡先
-(電話)</t>
+          <t>工務店担当者</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>連絡先
-(メール)</t>
+          <t>電話</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>連絡手段
 (LINE/電話/メール)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>物件所在地</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>物件タイプ</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>撮影希望日</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>撮影確定日</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>撮影ステータス</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>カメラマン</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>編集ステータス</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>YouTube公開日</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>サイト掲載日</t>
+          <t>公開/掲載日</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>掲載先</t>
+          <t>ヒアリング済</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -612,7 +625,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -634,7 +647,7 @@
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
@@ -656,7 +669,7 @@
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -678,7 +691,7 @@
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
@@ -700,7 +713,7 @@
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -722,7 +735,7 @@
       <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
@@ -744,7 +757,7 @@
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
@@ -766,7 +779,7 @@
       <c r="Q11" s="4" t="inlineStr"/>
       <c r="R11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
@@ -788,7 +801,7 @@
       <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" s="4" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -810,7 +823,7 @@
       <c r="Q13" s="4" t="inlineStr"/>
       <c r="R13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
@@ -832,7 +845,7 @@
       <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" s="4" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -854,7 +867,7 @@
       <c r="Q15" s="4" t="inlineStr"/>
       <c r="R15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -876,7 +889,7 @@
       <c r="Q16" s="4" t="inlineStr"/>
       <c r="R16" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
@@ -898,7 +911,7 @@
       <c r="Q17" s="4" t="inlineStr"/>
       <c r="R17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
@@ -920,7 +933,7 @@
       <c r="Q18" s="4" t="inlineStr"/>
       <c r="R18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -942,7 +955,7 @@
       <c r="Q19" s="4" t="inlineStr"/>
       <c r="R19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
@@ -964,7 +977,7 @@
       <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
@@ -986,7 +999,7 @@
       <c r="Q21" s="4" t="inlineStr"/>
       <c r="R21" s="4" t="inlineStr"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
@@ -1008,7 +1021,7 @@
       <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
@@ -1030,7 +1043,7 @@
       <c r="Q23" s="4" t="inlineStr"/>
       <c r="R23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
@@ -1055,91 +1068,14 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>【撮影ステータス】</t>
+          <t>【撮影ステータス】依頼受付 → 日程調整中 → 撮影日確定 → 撮影済 → 編集中 → レビュー待ち → 納品済 → 掲載済</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>・依頼受付</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>・日程調整中</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>・撮影日確定</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>・撮影済</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>・編集中</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>・レビュー待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>・納品済</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>・掲載済</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>【掲載先の選択肢】</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>・動画コンテンツ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>・事例ライブラリ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>・動画+事例 両方</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>【掲載先】動画コンテンツ (/videos) / 事例ライブラリ (/case-studies) / 両方</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1109,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>撮影スケジュール (月次)</t>
@@ -1183,11 +1119,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>月ごとの撮影予定を管理。カメラマン・工務店とのスケジュール調整用</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>月ごとの撮影予定管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -1239,7 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -1253,7 +1189,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
@@ -1267,7 +1203,7 @@
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -1281,7 +1217,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
@@ -1295,7 +1231,7 @@
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -1309,7 +1245,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
@@ -1323,7 +1259,7 @@
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
@@ -1337,7 +1273,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
@@ -1351,7 +1287,7 @@
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -1365,7 +1301,7 @@
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
@@ -1379,7 +1315,7 @@
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -1393,7 +1329,7 @@
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -1407,7 +1343,7 @@
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
@@ -1421,7 +1357,7 @@
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
@@ -1435,7 +1371,7 @@
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -1449,7 +1385,7 @@
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
@@ -1463,7 +1399,7 @@
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
@@ -1477,7 +1413,7 @@
       <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
@@ -1491,7 +1427,7 @@
       <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
@@ -1505,7 +1441,7 @@
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
@@ -1519,7 +1455,7 @@
       <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="inlineStr"/>
     </row>
-    <row r="25" ht="22" customHeight="1">
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
@@ -1533,7 +1469,7 @@
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
@@ -1547,7 +1483,7 @@
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
@@ -1561,7 +1497,7 @@
       <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr"/>
     </row>
-    <row r="28" ht="22" customHeight="1">
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
@@ -1575,7 +1511,7 @@
       <c r="I28" s="4" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr"/>
     </row>
-    <row r="29" ht="22" customHeight="1">
+    <row r="29" ht="24" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
@@ -1589,7 +1525,7 @@
       <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="4" t="inlineStr"/>
     </row>
-    <row r="30" ht="22" customHeight="1">
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
@@ -1603,7 +1539,7 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
     </row>
-    <row r="31" ht="22" customHeight="1">
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
@@ -1617,7 +1553,7 @@
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
     </row>
-    <row r="32" ht="22" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
@@ -1631,7 +1567,7 @@
       <c r="I32" s="4" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr"/>
     </row>
-    <row r="33" ht="22" customHeight="1">
+    <row r="33" ht="24" customHeight="1">
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
@@ -1645,7 +1581,7 @@
       <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr"/>
     </row>
-    <row r="34" ht="22" customHeight="1">
+    <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
@@ -1689,7 +1625,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>撮影関連 連絡先一覧</t>
@@ -1699,11 +1635,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>工務店担当・カメラマン・編集者の連絡先を一元管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>工務店・カメラマン・編集者の連絡先を一元管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -1731,7 +1667,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>メール</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1755,267 +1691,227 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="n">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>ハウスサポート</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>万代ホーム</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr"/>
-      <c r="J6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>ベルハウジング</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>タマルハウス</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="n">
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>感動ハウス</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="n">
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>七呂建設</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>ヤマサハウス</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="n">
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>大分建設</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="n">
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>(工務店9)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="7" t="n">
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>(工務店10)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>撮影窓口</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -2026,14 +1922,10 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>(メインカメラマン)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>撮影・動画</t>
-        </is>
-      </c>
+          <t>(メイン)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr"/>
@@ -2041,7 +1933,7 @@
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -2052,14 +1944,10 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>(サブカメラマン)</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>撮影・写真</t>
-        </is>
-      </c>
+          <t>(サブ)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr"/>
@@ -2067,7 +1955,7 @@
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
@@ -2081,11 +1969,7 @@
           <t>(動画編集)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>動画編集</t>
-        </is>
-      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
@@ -2093,7 +1977,7 @@
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
@@ -2107,11 +1991,7 @@
           <t>(写真レタッチ)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>写真編集</t>
-        </is>
-      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr"/>
@@ -2119,7 +1999,7 @@
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -2130,14 +2010,10 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむ代表</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>撮影ディレクション</t>
-        </is>
-      </c>
+          <t>代表</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr"/>
@@ -2145,7 +2021,7 @@
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
@@ -2156,14 +2032,10 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむ PM</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>スケジュール管理</t>
-        </is>
-      </c>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr"/>
@@ -2186,505 +2058,876 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>撮影ヒアリングシート (動画コンテンツ用)</t>
+          <t>撮影ヒアリングシート (動画コンテンツ /videos 用)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>撮影前に工務店から収集する情報。回答内容は /videos の動画詳細ページに反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>このシートの回答内容は src/lib/videos-data.ts の VideoData 型に直接反映されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ヒアリング項目</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>入力例 / 選択肢</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>コード反映先
+(videos-data.ts)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>画面表示箇所
+(/videos ページ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>■ VideoData 型の必須フィールド（これがないと /videos に掲載できません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>動画タイトル</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>「小さなかわいい平屋」等、YouTube と同じタイトル</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>動画カードのタイトル
+動画詳細ページの見出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>YouTube 動画 ID</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>例: 0gxkNh2BC0A (YouTube URL の v= 以降)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>youtubeId</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>動画埋め込み
+サムネイル画像の自動取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>再生回数 (表示用テキスト)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>例: 99万回再生</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>views</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>動画カードの再生回数バッジ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>再生回数 (数値)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>例: 990000 (ソート・ランキング用)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>viewCount</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>人気順ソート
+TOP PICKUP 選定</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ヒアリング項目</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>反映先フィールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>物件タイトル (動画タイトルに使用)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>YouTube 動画 ID (公開済みの場合)</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>youtubeId</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>物件所在地 (都道府県)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ルームツアー / 取材 / 解説 / トレンド から1つ</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>動画一覧のフィルター
+動画カードのタグ表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>例: 鹿児島県</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>prefecture</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>動画カードの地域表示
+エリア検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>施工会社名</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>例: ハウスサポート (builders-data.ts の name と一致させる)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>builder</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>動画詳細「この家を建てた工務店」
+工務店詳細への遷移リンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>建物坪数</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>例: 25 (数値のみ、「坪」は不要)</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>tsubo</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>動画カテゴリ (ルームツアー/取材/解説/トレンド)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>動画カードの坪数表示
+事例ライブラリとの紐付け</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>■ 撮影・編集に必要な情報（コードには直接反映しないが撮影品質に影響）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>撮影の見どころ (この家の最大の特徴は?)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>(ナレーション用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>この家の最大の特徴・見どころ (3つ)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>① 回遊動線 ② 吹き抜けLDK ③ 中庭</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>ナレーション原稿に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>施主様のこだわりポイント (3つ)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>(ナレーション用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>施主様のこだわりポイント</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>キッチンの高さと収納量にこだわった</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>ナレーション・テロップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>使用している主な建材・設備メーカー</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>(テロップ用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>LIXIL キッチン / YKKap 窓 等</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>テロップ表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>断熱・気密の仕様 (UA値/C値/等級)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>(テロップ用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>断熱・気密の仕様</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>UA値 0.46 / C値 0.5 / 断熱等級 6</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>テロップ・ナレーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>坪単価の目安 (公開可なら)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>約 65万円/坪</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>テロップ表示 (任意)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>撮影内容</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>特に撮影してほしい場所・アングル</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>(カメラマン指示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>LDK全景 / キッチンからの眺め / 外観夕景</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン指示書</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>撮影内容</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>撮影 NG の場所・映してはいけないもの</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>(カメラマン指示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>隣家の窓 / 施主の私物 / 住所表示</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン指示書</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>撮影内容</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BGM のイメージ</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>おしゃれ / ナチュラル / モダン / おまかせ</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>編集者指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>施主情報</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>施主様の撮影立ち会い可否</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>(スケジュール用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>可 / 不可 / 部分的に可</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール調整</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>施主情報</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>施主コメントの撮影可否 (顔出し/声のみ/不可)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>(編集用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>施主コメントの撮影可否</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>顔出しOK / 声のみ / 不可</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>編集判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>施主情報</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>施主様の家族構成 (動画内で紹介する場合)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>(ナレーション用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>施主様の家族構成 (紹介する場合)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>夫婦 + 子ども2人</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>ナレーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>撮影条件</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>撮影可能な日程 (候補 3 日程)</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>(スケジュール用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>5/10, 5/15, 5/20</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>撮影条件</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>撮影可能な時間帯</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>(スケジュール用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>10:00〜16:00</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>撮影条件</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>駐車場の有無 (撮影車両)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>(ロケハン用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>駐車場の有無</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>あり (2台分) / なし</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>ロケハン</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>撮影条件</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>近隣への撮影許可の要否</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>(事前準備)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>ドローン撮影の可否 (航空法対応)</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>(カメラマン確認)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>ドローン撮影の可否</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>可 / 不可 / 要確認</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>YouTube 公開の承認者 (施主 or 工務店)</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>(公開フロー)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>YouTube 公開の最終承認者</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>施主 / 工務店 / 両方</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>公開フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>サムネイル画像の希望 (特定のアングル等)</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>(編集用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>サムネイル画像の希望アングル</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>外観正面 / LDK / おまかせ</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>編集者指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>公開前のプレビュー確認の希望</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>(公開フロー)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>公開前プレビュー確認の希望</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>あり / なし</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>公開フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>ぺいほーむサイト (/videos) への掲載許可</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>(掲載確認)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ぺいほーむサイト (/videos) 掲載許可</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>掲載判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>SNS (X/Instagram/Threads) での拡散許可</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>(SNS運用)</t>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>SNS 拡散許可 (X/Instagram/Threads)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>全許可 / 一部 / 不可</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>SNS 運用</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2696,33 +2939,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>撮影ヒアリングシート (平屋事例ライブラリ用)</t>
+          <t>撮影ヒアリングシート (平屋事例ライブラリ /case-studies 用)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>撮影前に工務店から収集する情報。回答内容は /case-studies の個別ページに反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>このシートの回答内容は src/lib/case-studies-data.ts の CaseStudy 型に直接反映されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
+          <t>セクション</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2732,703 +2977,1685 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>入力例 / 選択肢</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>回答</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>反映先フィールド</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>コード反映先
+(case-studies-data.ts)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>画面表示箇所
+(/case-studies/[id])</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>事例タイトル (掲載名)</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+          <t>■ CaseStudy 型の必須フィールド（これがないと /case-studies に掲載できません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>事例タイトル</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>「完璧な間取りのお洒落で超かわいい平屋」</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>施工会社名</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー見出し
+パンくず
+一覧カードタイトル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>施工会社 ID</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>builders-data.ts の id と一致させる (例: builder-3)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>builderId</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>完成年月 (YYYY-MM)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>「施工会社」セクション
+工務店ページへのリンク
+「○○の見学会を予約」CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>完成年月</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03 (YYYY-MM 形式)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>completedAt</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>所在地 (都道府県 + 市区町村)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>prefecture, city</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>建物スペック</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>間取り (1LDK / 2LDK / 3LDK / 4LDK / 5LDK+)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>ヒーローの「○○完成」表示
+物件情報テーブル「完成時期」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>所在地 (都道府県)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>prefecture</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー「鹿児島県 鹿児島市」
+物件情報テーブル「所在地」</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>所在地 (市区町村)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島市</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>間取り</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1LDK / 2LDK / 3LDK / 4LDK / 5LDK+ から1つ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>layout</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>建物スペック</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー統計「間取り」
+物件情報テーブル「間取り」
+間取り図セクションのラベル
+一覧のフィルター</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>建物坪数</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>28 (数値のみ)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>tsubo</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>建物スペック</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー統計「建物 28坪」
+物件情報テーブル「建物面積」
+間取り図ラベル</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>建物面積 (㎡)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>buildingArea</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>建物スペック</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー統計「(92.7㎡)」
+物件情報テーブル
+間取り図の各部屋面積計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>敷地面積 (㎡)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>184.8</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>landArea</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>費用情報</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>建物本体価格 (万円・税抜)</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー統計「敷地 184.8㎡」
+物件情報テーブル「敷地面積」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>建物本体価格 (万円)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>buildingPrice</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>費用情報</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>土地価格 (万円、土地ありの場合)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー統計「本体価格 2,310万円」
+費用内訳テーブル「建物本体価格」
+諸費用の自動計算 (×8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>土地価格 (万円、土地ありなら)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>900 (土地ありの場合) / 空欄 (土地なし)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>landPrice</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>費用情報</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>総額 (建物+土地+諸費用、万円)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>費用内訳テーブル「土地価格」
+(null なら「土地あり」と表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>総額 (万円)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>3391 (建物+土地+諸費用)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>totalPrice</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>費用情報</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>価格情報の公開可否 (全公開/本体のみ/非公開)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>(掲載判断)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>施主情報</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>家族構成 (夫婦2人 / 夫婦+子ども1人 等)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー最上部の大きな数字
+費用内訳テーブル「総額」
+一覧カードの価格表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>家族構成</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>夫婦 + 子ども1人</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>familyStructure</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>施主情報</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>施主コメント (掲載用、100〜200文字)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>ヒーロー「夫婦 + 子ども1人」
+物件情報テーブル「家族構成」
+施主コメント末尾の署名</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>キャッチコピー (1行)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>「家族の暮らしに寄り添う、28坪の3LDK平屋」</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>catchphrase</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>パンくず下のサブタイトル</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>事例の説明 (200〜300文字)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>「○○が手掛けた28坪の3LDK。…ぺいほーむ注目の完成事例です。」</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>ヒーローの説明文 (タイトル下)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>設計のポイント①</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>「回遊動線で家事効率を最大化」等</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>designPoints[0]</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>「設計のポイント」セクション カード①</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>設計のポイント②</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>「高断熱サッシで光を取り込みながら断熱」</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>designPoints[1]</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>「設計のポイント」セクション カード②</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>設計のポイント③</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>「シューズクロークからパントリーへの直結動線」</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>designPoints[2]</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>「設計のポイント」セクション カード③</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>施主コメント (100〜200文字)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>「初めての家づくりで不安でしたが…」</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>ownerComment</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>施主情報</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>「施主様の声」セクション (引用表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>特徴タグ (複数、カンマ区切り)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>平屋, 高性能, 回遊動線, 中庭, ZEH</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>「特徴タグ」セクション (#タグ表示)
+一覧のタグフィルター</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>■ 写真データ（photos フィールド — 外観8枚 + 内観12枚 = 20枚）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>外観 正面 (メインビジュアル)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>建物全体が入る正面アングル</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>photos[0] exterior</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ
+メイン画像 (デフォルト表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>外観 全体 (斜めアングル)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>建物の立体感がわかる角度</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>photos[1] exterior</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>外観 玄関アプローチ</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>門扉〜玄関ドアまでの動線</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>photos[2] exterior</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>外観 庭側</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>ウッドデッキ・庭・テラスが見える角度</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>photos[3] exterior</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>外観 夕景</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>照明が映える夕方〜夜の外観 (撮影可能なら)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>photos[4] exterior</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>外観 駐車場側</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>カーポート・駐車スペースが見える角度</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>photos[5] exterior</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>外観 屋根</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>屋根形状・太陽光パネルが見える角度</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>photos[6] exterior</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>外観写真</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>外観 植栽・外構</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>庭の植栽・フェンス・アプローチ</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>photos[7] exterior</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>LDK 全体</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>リビング・ダイニング・キッチンが一望できるアングル</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>photos[8] interior</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ
+メイン画像 (内観選択時)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>キッチン正面 (設備・収納が見える角度)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>photos[9] interior</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>ダイニング</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>食卓スペース・窓からの採光</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>photos[10] interior</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>リビング</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>ソファ方向からの眺め・テレビ壁面</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>photos[11] interior</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>主寝室</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ベッド配置・WIC入口が見える角度</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>photos[12] interior</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>洋室 (子ども部屋等)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>広さ・窓・収納がわかるアングル</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>photos[13] interior</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>WIC・収納</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>ウォークインクローゼット or 大型収納</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>photos[14] interior</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>洗面脱衣室</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>洗面台・鏡・収納</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>photos[15] interior</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>浴室</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>浴槽・シャワー・窓</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>photos[16] interior</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>便器・手洗い・アクセントクロス</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>photos[17] interior</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>玄関ホール</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>玄関ドアを開けた時の第一印象</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>photos[18] interior</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>内観写真</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>ウッドデッキ/テラス</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>屋外リビング・BBQスペース</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>photos[19] interior</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「内観」タブ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>■ 間取り図（会員限定セクション）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>間取り図データの提供形式</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>PDF / CAD / 紙 / なし</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>「間取り図」セクション
+(会員のみフル表示
+非会員はブラー+登録CTA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>間取り図の掲載許可</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>間取り図セクション表示判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>各部屋の面積 (わかれば)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>LDK 37㎡ / 主寝室 14㎡ / 洋室 8㎡ 等</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>SVG 間取り図の面積ラベル</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>特記事項 (スキップフロア等)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ロフトあり / 小上がり和室 等</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>間取り図の注記</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>■ 撮影・掲載条件（コードには直接反映しないが運用に必要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能な日程 (候補 3 日程)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>5/10, 5/15, 5/20</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能な時間帯</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>10:00〜16:00</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>駐車場の有無 (撮影車両)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>あり (2台分) / なし</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>ロケハン</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>鍵の受け渡し方法 (OB宅の場合)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>工務店が開錠 / 施主在宅</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>事前準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>家具・家電の配置状態</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>入居前 (空室) / 入居後 (家具あり)</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>写真の雰囲気決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>インテリア小物のセッティング</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>工務店が準備 / ぺいほーむが持参 / なし</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>事前準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>撮影 NG の場所</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>隣家の窓 / 施主の私物 / 住所表示</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>ぺいほーむ /case-studies への掲載許可</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>掲載判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>価格情報の公開範囲</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>全公開 / 本体のみ / 非公開</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>費用内訳セクションの表示制御</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>施主の顔写真掲載可否</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>(写真選定用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>キャッチコピー (1行、事例の魅力を要約)</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>catchphrase</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>事例の説明 (200〜300文字)</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>設計のポイント① (動線・収納・採光等)</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>designPoints[0]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>設計のポイント②</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>designPoints[1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>設計のポイント③</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>designPoints[2]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>設計情報</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>特徴タグ (平屋/高性能/ZEH/ローコスト/自然素材 等、複数可)</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>外観写真の撮影アングル希望 (正面/庭側/夕景 等)</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>photos (exterior)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>外観で特に見せたいポイント</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>photos (exterior)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>内観で特に撮影してほしい場所 (LDK/キッチン/主寝室 等)</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>photos (interior)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>撮影 NG の場所・映してはいけないもの</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>(カメラマン指示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>撮影時のインテリア・小物のセッティング有無</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>(事前準備)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>写真撮影</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>家具・家電の配置状態 (入居前/入居後)</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr"/>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>(写真選定用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>間取り図</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>間取り図データの提供可否 (PDF/CAD/紙)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr"/>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>(間取り図セクション)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>間取り図</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>間取り図の掲載許可 (会員限定で掲載)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr"/>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>(間取り図セクション)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>間取り図</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>間取り図に記載してほしい情報 (寸法/収納名称 等)</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr"/>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>(間取り図セクション)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>撮影可能な日程 (候補 3 日程)</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr"/>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>(スケジュール用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>撮影可能な時間帯</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>(スケジュール用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>駐車場の有無 (撮影車両)</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>(ロケハン用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>鍵の受け渡し方法 (OB宅の場合)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>(事前準備)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>可 / 不可</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>施主コメントセクション</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>ぺいほーむサイト (/case-studies) への掲載許可</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr"/>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>(掲載確認)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>掲載前プレビュー確認の希望</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>あり / なし</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>公開フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>掲載前のプレビュー確認の希望</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr"/>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>(公開フロー)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>SNS 写真使用許可 (X/Instagram/Threads)</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>全許可 / 一部 / 不可</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>SNS 運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>SNS での写真使用許可</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr"/>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>(SNS運用)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>掲載後の修正・削除依頼の窓口</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr"/>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>(運用)</t>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>工務店担当○○ / メール / 電話</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>運用</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="6">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3440,7 +4667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3451,7 +4678,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>納品・掲載チェックリスト</t>
@@ -3465,7 +4692,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -3497,7 +4724,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -3523,7 +4750,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
@@ -3534,7 +4761,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>撮影データの受け渡し完了 (クラウド or HDD)</t>
+          <t>撮影データの受け渡し完了</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3549,13 +4776,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>編集 (動画)</t>
+          <t>編集(動画)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3570,23 +4797,23 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>撮影後 1 週間</t>
+          <t>撮影後1週間</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>編集 (動画)</t>
+          <t>編集(動画)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>BGM/SE のライセンス確認</t>
+          <t>サムネイル作成完了</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3601,70 +4828,70 @@
       </c>
       <c r="F8" s="4" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>編集 (動画)</t>
+          <t>編集(写真)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>サムネイル作成完了</t>
+          <t>写真セレクト (外観8枚+内観12枚=20枚)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>編集者</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>公開前</t>
+          <t>撮影後3日</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>編集 (写真)</t>
+          <t>編集(写真)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>写真セレクト (外観8枚 + 内観12枚 = 20枚)</t>
+          <t>写真レタッチ完了 (明るさ/色調/水平)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>編集者</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>撮影後 3 日</t>
+          <t>撮影後5日</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>編集 (写真)</t>
+          <t>編集(写真)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>写真レタッチ完了 (明るさ/色調/水平)</t>
+          <t>写真リサイズ (Web用800x600+高解像度)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3674,38 +4901,38 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>撮影後 5 日</t>
+          <t>撮影後5日</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>編集 (写真)</t>
+          <t>レビュー</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>写真リサイズ (Web用 800x600 + 高解像度)</t>
+          <t>工務店による動画プレビュー確認OK</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>編集者</t>
+          <t>営業</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>撮影後 5 日</t>
+          <t>公開3日前</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -3716,7 +4943,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>工務店による動画プレビュー確認 OK</t>
+          <t>工務店による写真確認OK</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3726,12 +4953,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>公開 3 日前</t>
+          <t>掲載3日前</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
@@ -3742,7 +4969,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>工務店による写真確認 OK</t>
+          <t>施主による確認OK (必要な場合)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -3752,12 +4979,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>掲載 3 日前</t>
+          <t>公開3日前</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -3768,59 +4995,59 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>施主による確認 OK (必要な場合)</t>
+          <t>NG箇所の修正完了</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>編集者</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>公開 3 日前</t>
+          <t>公開1日前</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>NG 箇所の修正完了</t>
+          <t>YouTube アップロード完了</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>編集者</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>公開 1 日前</t>
+          <t>公開日</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>公開 (動画)</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>YouTube アップロード完了</t>
+          <t>YouTube タイトル・説明文・タグ設定</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3835,23 +5062,23 @@
       </c>
       <c r="F17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>公開 (動画)</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>YouTube タイトル・説明文・タグ設定</t>
+          <t>videos-data.ts に新規エントリ追加</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>エンジニア</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -3861,23 +5088,23 @@
       </c>
       <c r="F18" s="4" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>公開 (動画)</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむ /videos への掲載データ更新</t>
+          <t>/videos で表示確認 (PC+モバイル)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>エンジニア</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3887,18 +5114,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>掲載 (事例)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>事例データ作成 (ヒアリング回答を反映)</t>
+          <t>ヒアリングシート⑤の全回答をデータ化</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3913,18 +5140,18 @@
       </c>
       <c r="F20" s="4" t="inlineStr"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>掲載 (事例)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>写真を Supabase Storage にアップロード</t>
+          <t>case-studies-data.ts に新規エントリ追加</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3939,18 +5166,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>掲載 (事例)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>間取り図データの登録 (会員限定)</t>
+          <t>写真20枚を Supabase Storage にアップロード</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -3965,18 +5192,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>掲載 (事例)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむ /case-studies への掲載データ更新</t>
+          <t>間取り図データの登録 (会員限定)</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -3991,18 +5218,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
+    <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>掲載 (事例)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>掲載後の表示確認 (PC + モバイル)</t>
+          <t>/case-studies/[id] で全セクション表示確認</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4017,83 +5244,109 @@
       </c>
       <c r="F24" s="4" t="inlineStr"/>
     </row>
-    <row r="25" ht="22" customHeight="1">
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>X/Instagram/Threads での告知投稿</t>
+          <t>写真ギャラリー 外観/内観タブ動作確認</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>代表</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>掲載翌日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>LINE 公式での告知配信</t>
+          <t>間取り図 会員/非会員の表示切替確認</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>代表</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>掲載翌日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>X/Instagram/Threads での告知投稿</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>代表</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>掲載翌日</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>請求</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>撮影費 ¥150,000 の請求書発行 (Phase 2〜)</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>経理</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>撮影月末</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/最新版/02_管理シート/撮影案件管理_ヒアリングシート.xlsx
+++ b/docs/最新版/02_管理シート/撮影案件管理_ヒアリングシート.xlsx
@@ -58,7 +58,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -103,11 +108,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -121,12 +170,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -544,8 +594,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>掲載先
-(動画/事例/両方)</t>
+          <t>掲載先</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -555,7 +604,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>工務店担当者</t>
+          <t>担当者</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -570,8 +619,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>連絡手段
-(LINE/電話/メール)</t>
+          <t>連絡手段</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -596,7 +644,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>撮影ステータス</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1064,20 +1112,6 @@
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>【撮影ステータス】依頼受付 → 日程調整中 → 撮影日確定 → 撮影済 → 編集中 → レビュー待ち → 納品済 → 掲載済</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>【掲載先】動画コンテンツ (/videos) / 事例ライブラリ (/case-studies) / 両方</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1112,7 +1146,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>撮影スケジュール (月次)</t>
+          <t>撮影スケジュール</t>
         </is>
       </c>
     </row>
@@ -1692,224 +1726,224 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>ハウスサポート</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>万代ホーム</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>ベルハウジング</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>タマルハウス</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>感動ハウス</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>七呂建設</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>ヤマサハウス</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>大分建設</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>(工務店9)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>工務店</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>(工務店10)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -1966,7 +2000,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>(動画編集)</t>
+          <t>(動画)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
@@ -1988,7 +2022,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>(写真レタッチ)</t>
+          <t>(写真)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -2058,28 +2092,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>撮影ヒアリングシート (動画コンテンツ /videos 用)</t>
+          <t>撮影ヒアリングシート (動画コンテンツ /videos 用) — 完全版</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>このシートの回答内容は src/lib/videos-data.ts の VideoData 型に直接反映されます</t>
+          <t>回答は src/lib/properties.ts の PropertyData 型 + src/lib/videos-data.ts の VideoData 型に反映</t>
         </is>
       </c>
     </row>
@@ -2106,28 +2140,31 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>コード反映先
-(videos-data.ts)</t>
+          <t>コード反映先</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>画面表示箇所
-(/videos ページ)</t>
+          <t>画面表示箇所</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>■ VideoData 型の必須フィールド（これがないと /videos に掲載できません）</t>
-        </is>
-      </c>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>■ 基本情報 (VideoData 型 → /videos 一覧に表示)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -2137,26 +2174,25 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>「小さなかわいい平屋」等、YouTube と同じタイトル</t>
+          <t>「小さなかわいい平屋」</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>動画カードのタイトル
-動画詳細ページの見出し</t>
+          <t>動画カード / 動画詳細見出し / パンくず</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -2166,40 +2202,39 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>例: 0gxkNh2BC0A (YouTube URL の v= 以降)</t>
+          <t>0gxkNh2BC0A (URLのv=以降)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>youtubeId</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>動画埋め込み
-サムネイル画像の自動取得</t>
+          <t>動画埋め込み iframe / サムネイル自動取得</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>再生回数 (表示用テキスト)</t>
+          <t>再生回数 (テキスト)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>例: 99万回再生</t>
+          <t>99万回再生</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>views</t>
         </is>
@@ -2213,7 +2248,7 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -2223,26 +2258,25 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>例: 990000 (ソート・ランキング用)</t>
+          <t>990000</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>viewCount</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>人気順ソート
-TOP PICKUP 選定</t>
+          <t>人気順ソート / TOP PICKUP選定</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -2252,26 +2286,25 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ルームツアー / 取材 / 解説 / トレンド から1つ</t>
+          <t>ルームツアー / 取材 / 解説 / トレンド</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>動画一覧のフィルター
-動画カードのタグ表示</t>
+          <t>一覧フィルター / カードタグ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2281,26 +2314,25 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>例: 鹿児島県</t>
+          <t>鹿児島県</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>prefecture</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>動画カードの地域表示
-エリア検索</t>
+          <t>カード地域表示 / エリア検索</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -2310,26 +2342,25 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>例: ハウスサポート (builders-data.ts の name と一致させる)</t>
+          <t>ハウスサポート</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>builder</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>動画詳細「この家を建てた工務店」
-工務店詳細への遷移リンク</t>
+          <t>「この家を建てた工務店」セクション / リンク</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>基本情報</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2339,594 +2370,1872 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>例: 25 (数値のみ、「坪」は不要)</t>
+          <t>25 (数値のみ)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>tsubo</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>動画カードの坪数表示
-事例ライブラリとの紐付け</t>
+          <t>カード坪数表示 / 事例紐付け</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>■ 撮影・編集に必要な情報（コードには直接反映しないが撮影品質に影響）</t>
-        </is>
-      </c>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>■ 価格・コスト情報 (PropertyData.priceBreakdown → 「価格・コスト情報」カード)</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>この家の最大の特徴・見どころ (3つ)</t>
+          <t>総額 (税込表示用)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>① 回遊動線 ② 吹き抜けLDK ③ 中庭</t>
+          <t>1,980万円</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>price</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>ナレーション原稿に使用</t>
+          <t>価格カードの大きな金額表示</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>施主様のこだわりポイント</t>
+          <t>建物本体価格</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>キッチンの高さと収納量にこだわった</t>
+          <t>1,580万円</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>priceBreakdown.building</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ナレーション・テロップ</t>
+          <t>内訳テーブル「建物本体」行</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>使用している主な建材・設備メーカー</t>
+          <t>土地価格</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>LIXIL キッチン / YKKap 窓 等</t>
+          <t>280万円 (土地込みの場合)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>priceBreakdown.land</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>テロップ表示</t>
+          <t>内訳テーブル「土地」行</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>断熱・気密の仕様</t>
+          <t>諸費用</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>UA値 0.46 / C値 0.5 / 断熱等級 6</t>
+          <t>120万円</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>priceBreakdown.misc</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>テロップ・ナレーション</t>
+          <t>内訳テーブル「諸費用」行</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>価格</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>坪単価の目安 (公開可なら)</t>
+          <t>坪単価</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>約 65万円/坪</t>
+          <t>63.2万円</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>priceBreakdown.perTsubo</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>テロップ表示 (任意)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>撮影内容</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>特に撮影してほしい場所・アングル</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>LDK全景 / キッチンからの眺め / 外観夕景</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>カメラマン指示書</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>撮影内容</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>撮影 NG の場所・映してはいけないもの</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>隣家の窓 / 施主の私物 / 住所表示</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>カメラマン指示書</t>
-        </is>
-      </c>
+          <t>内訳テーブル「坪単価」行</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>■ 物件概要 (PropertyData → 「物件概要」カード)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>撮影内容</t>
+          <t>物件概要</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BGM のイメージ</t>
+          <t>間取り</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>おしゃれ / ナチュラル / モダン / おまかせ</t>
+          <t>3LDK</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>layout</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>編集者指示</t>
+          <t>概要カード「間取り」/ 間取り図ラベル</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>物件概要</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>延床面積</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>25坪（82.6㎡）</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>概要カード「延床面積」/ 間取り図ラベル</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>施主情報</t>
+          <t>物件概要</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>施主様の撮影立ち会い可否</t>
+          <t>敷地面積</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>可 / 不可 / 部分的に可</t>
+          <t>60坪（198㎡）</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>landArea</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>スケジュール調整</t>
+          <t>概要カード「敷地面積」</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>施主情報</t>
+          <t>物件概要</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>施主コメントの撮影可否</t>
+          <t>建ぺい率</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>顔出しOK / 声のみ / 不可</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>buildingCoverage</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>編集判断</t>
+          <t>概要カード「建ぺい率」</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>施主情報</t>
+          <t>物件概要</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>施主様の家族構成 (紹介する場合)</t>
+          <t>容積率</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>夫婦 + 子ども2人</t>
+          <t>200%</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>floorAreaRatio</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>ナレーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>撮影可能な日程 (候補 3 日程)</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>5/10, 5/15, 5/20</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>撮影条件</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>撮影可能な時間帯</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>10:00〜16:00</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
+          <t>概要カード「容積率」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>物件概要</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>構造</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>木造軸組 等</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>specs.structure</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>概要カード「構造」</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>■ 土地・法規情報 (PropertyData → 「土地・法規情報」カード)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>撮影条件</t>
+          <t>土地・法規</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>駐車場の有無</t>
+          <t>地形</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>あり (2台分) / なし</t>
+          <t>平坦地 / 傾斜地 / 旗竿地 等</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>terrain</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>ロケハン</t>
+          <t>土地カード「地形」</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>撮影条件</t>
+          <t>土地・法規</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ドローン撮影の可否</t>
+          <t>道路接面</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>可 / 不可 / 要確認</t>
+          <t>南側6m公道 等</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>roadAccess</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>カメラマン確認</t>
+          <t>土地カード「接道」</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>土地・法規</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>用途地域</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>第一種住居地域 等</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>zoning</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>土地カード「用途地域」</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>掲載条件</t>
+          <t>土地・法規</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>YouTube 公開の最終承認者</t>
+          <t>地目</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>施主 / 工務店 / 両方</t>
+          <t>宅地 / 田 / 畑 等</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>landCategory</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>公開フロー</t>
+          <t>土地カード「地目」</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>掲載条件</t>
+          <t>土地・法規</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>サムネイル画像の希望アングル</t>
+          <t>建築条件</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>外観正面 / LDK / おまかせ</t>
+          <t>なし / あり (条件付き)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>buildingCondition</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>編集者指示</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>公開前プレビュー確認の希望</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>あり / なし</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>公開フロー</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>ぺいほーむサイト (/videos) 掲載許可</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>許可 / 不可</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>掲載判断</t>
-        </is>
-      </c>
+          <t>土地カード「建築条件」</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>■ 設備情報 (PropertyData → 「主な設備」カード)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="8" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>キッチン メーカー</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>LIXIL / Panasonic / TOTO / タカラ 等</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>kitchen.maker</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>設備カード「キッチン」行</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>キッチン シリーズ</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>シエラS / ラクシーナ 等</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>kitchen.series</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>同上 (メーカー / シリーズ で表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>浴室 メーカー</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>TOTO / LIXIL / Panasonic 等</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>bath.maker</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>設備カード「浴室」行</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>浴室 サイズ</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>1616 / 1620 / 1818 等</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>bath.size</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>同上 (メーカー / サイズ で表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>トイレ メーカー</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>TOTO / LIXIL 等</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>toilet.maker</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>設備カード「トイレ」行</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>トイレ シリーズ</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ZJ2 / アメージュ 等</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>toilet.series</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>同上 (メーカー / シリーズ で表示)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>■ 性能情報 (PropertyData → 「住宅性能」セクション)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>断熱等級</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>等級5 / 等級6 / 等級7</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>insulation</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>性能バッジ「断熱等級」</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>UA値</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>0.56 (数値のみ、W/㎡K は自動付与)</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>uaValue</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>性能バッジ「UA値 0.56 W/㎡K」</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>性能</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>耐震等級</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>等級3 / 等級2 / 等級1</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>earthquake</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>性能バッジ「耐震等級」</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>■ 間取り図 (FloorPlanViewer → 会員限定セクション)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>間取り図データの提供形式</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>PDF / CAD / 紙 / なし</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>FloorPlanViewer</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>「間取り図」セクション (会員限定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>間取り図の掲載許可</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>セクション表示判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>各部屋の名称と面積</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>LDK 15畳 / 主寝室 8畳 等</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>FloorPlanSvg</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>SVG内の部屋名・面積ラベル</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>特記事項 (ロフト・スキップフロア等)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>ロフトあり / 小上がり和室</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>SVG内の注記</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>■ 写真 (PhotoSlideshow → 「写真ギャラリー」セクション)</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>写真の枚数 (目安)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>10〜20枚</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>photos[]</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリーのスライドショー</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>外観写真 (撮影アングル指示)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>正面 / 庭側 / 夕景 等</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>photos[]</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>ギャラリー内の外観写真</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>内観写真 (撮影場所指示)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>LDK / キッチン / 主寝室 等</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>photos[]</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>ギャラリー内の内観写真</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>撮影NG場所</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>隣家の窓 / 施主私物 / 住所表示</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン指示書</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>■ 設計のポイント・担当者メモ (PropertyData → 各セクション)</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>この家のポイント① (設計の特徴)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>回遊動線で家事効率を最大化</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>points[0]</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>「この家のポイント」セクション ①</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>この家のポイント②</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>高断熱サッシで光を取り込みながら断熱</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr"/>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>points[1]</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>同上 ②</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>この家のポイント③</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>シューズクロークからパントリー直結</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>points[2]</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>同上 ③</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>この家のポイント④ (あれば)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>points[3]</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>同上 ④ (任意)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>担当者の氏名</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>山田太郎</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>designerMemo.name</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>「担当者メモ」セクション 氏名</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>担当者の役職</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>設計責任者</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>designerMemo.role</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>同上 役職</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>担当者のコメント (100〜200文字)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>この家は施主様の…</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>designerMemo.comment</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>同上 コメント本文</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>■ 施工会社情報 (PropertyData.builder → 「施工会社」セクション)</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="8" t="n"/>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>会社名</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>ハウスサポート</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>builder.name</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>施工会社カード 見出し</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島県鹿児島市中央町10-2</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>builder.location</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「所在地」</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>得意分野</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>平屋・ローコスト住宅</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>builder.specialty</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「得意分野」</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>会社紹介 (100〜200文字)</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島を拠点に…</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>builder.description</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>カード内の説明文</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>099-123-4567</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>builder.phone</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「電話番号」</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>ウェブサイト</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>https://example.com</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>builder.website</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「ウェブサイト」</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>創業年</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>2005年</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>builder.established</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「創業」</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>対応エリア</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>鹿児島県全域</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>builder.serviceArea</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>詳細テーブル「対応エリア」</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>工務店</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>特徴タグ (複数)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>平屋 / 自然素材 / 高性能</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>builder.features[]</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>工務店カード内のタグ表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>■ モデルハウス・見学会 (isModelHouse → 見学会予約セクション表示)</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>見学会</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>この物件はモデルハウスか</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>はい / いいえ</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>isModelHouse</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>true なら「この家の見学会を予約」セクション表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>見学会</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>見学会の開催日程 (あれば)</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>毎週土日 10:00-16:00 等</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>見学会予約セクション内の説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>■ 撮影・掲載条件 (コードに直接反映しない運用情報)</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="8" t="n"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能日程 (候補3日程)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>5/10, 5/15, 5/20</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能時間帯</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>10:00〜16:00</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr"/>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>駐車場の有無</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>あり (2台分) / なし</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>ロケハン</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>ドローン撮影の可否</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>可 / 不可 / 要確認</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>カメラマン確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>施主の撮影立ち会い可否</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>可 / 不可 / 部分的に可</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>施主コメント撮影可否</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>顔出しOK / 声のみ / 不可</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>編集判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
           <t>掲載条件</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>SNS 拡散許可 (X/Instagram/Threads)</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>YouTube公開の最終承認者</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>施主 / 工務店 / 両方</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr"/>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>公開フロー</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>サイト掲載許可</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>掲載判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>SNS拡散許可</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>全許可 / 一部 / 不可</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>SNS 運用</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>SNS運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>公開前プレビュー確認</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>あり / なし</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>公開フロー</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2939,28 +4248,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>撮影ヒアリングシート (平屋事例ライブラリ /case-studies 用)</t>
+          <t>撮影ヒアリングシート (平屋事例ライブラリ /case-studies 用) — 完全版</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>このシートの回答内容は src/lib/case-studies-data.ts の CaseStudy 型に直接反映されます</t>
+          <t>回答は src/lib/case-studies-data.ts の CaseStudy 型に反映</t>
         </is>
       </c>
     </row>
@@ -2987,23 +4296,26 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>コード反映先
-(case-studies-data.ts)</t>
+          <t>コード反映先</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>画面表示箇所
-(/case-studies/[id])</t>
+          <t>画面表示箇所</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>■ CaseStudy 型の必須フィールド（これがないと /case-studies に掲載できません）</t>
-        </is>
-      </c>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>■ CaseStudy 型の必須フィールド</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -3022,16 +4334,14 @@
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー見出し
-パンくず
-一覧カードタイトル</t>
+          <t>ヒーロー見出し / パンくず / 一覧カード</t>
         </is>
       </c>
     </row>
@@ -3048,20 +4358,18 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>builders-data.ts の id と一致させる (例: builder-3)</t>
+          <t>builder-3 (builders-data.ts の id)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>builderId</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>「施工会社」セクション
-工務店ページへのリンク
-「○○の見学会を予約」CTA</t>
+          <t>「施工会社」セクション / 工務店リンク / 見学会CTA</t>
         </is>
       </c>
     </row>
@@ -3078,19 +4386,18 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026-03 (YYYY-MM 形式)</t>
+          <t>2026-03 (YYYY-MM)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>completedAt</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>ヒーローの「○○完成」表示
-物件情報テーブル「完成時期」</t>
+          <t>ヒーロー「○○完成」/ 物件情報テーブル</t>
         </is>
       </c>
     </row>
@@ -3102,7 +4409,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>所在地 (都道府県)</t>
+          <t>都道府県</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3111,15 +4418,14 @@
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>prefecture</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー「鹿児島県 鹿児島市」
-物件情報テーブル「所在地」</t>
+          <t>ヒーロー / 物件情報「所在地」</t>
         </is>
       </c>
     </row>
@@ -3131,7 +4437,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>所在地 (市区町村)</t>
+          <t>市区町村</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3140,7 +4446,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>city</t>
         </is>
@@ -3164,21 +4470,18 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1LDK / 2LDK / 3LDK / 4LDK / 5LDK+ から1つ</t>
+          <t>1LDK/2LDK/3LDK/4LDK/5LDK+</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>layout</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー統計「間取り」
-物件情報テーブル「間取り」
-間取り図セクションのラベル
-一覧のフィルター</t>
+          <t>ヒーロー統計 / 物件情報 / 間取り図ラベル / フィルター</t>
         </is>
       </c>
     </row>
@@ -3195,20 +4498,18 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>28 (数値のみ)</t>
+          <t>28 (数値)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>tsubo</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー統計「建物 28坪」
-物件情報テーブル「建物面積」
-間取り図ラベル</t>
+          <t>ヒーロー統計「建物 28坪」/ 間取り図</t>
         </is>
       </c>
     </row>
@@ -3229,16 +4530,14 @@
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>buildingArea</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー統計「(92.7㎡)」
-物件情報テーブル
-間取り図の各部屋面積計算</t>
+          <t>ヒーロー統計 / 物件情報 / 間取り図面積計算</t>
         </is>
       </c>
     </row>
@@ -3259,15 +4558,14 @@
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>landArea</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー統計「敷地 184.8㎡」
-物件情報テーブル「敷地面積」</t>
+          <t>ヒーロー統計 / 物件情報</t>
         </is>
       </c>
     </row>
@@ -3288,16 +4586,14 @@
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>buildingPrice</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー統計「本体価格 2,310万円」
-費用内訳テーブル「建物本体価格」
-諸費用の自動計算 (×8%)</t>
+          <t>ヒーロー統計 / 費用内訳テーブル / 諸費用自動計算(×8%)</t>
         </is>
       </c>
     </row>
@@ -3309,24 +4605,23 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>土地価格 (万円、土地ありなら)</t>
+          <t>土地価格 (万円)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>900 (土地ありの場合) / 空欄 (土地なし)</t>
+          <t>900 / 空欄(土地なし)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>landPrice</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>費用内訳テーブル「土地価格」
-(null なら「土地あり」と表示)</t>
+          <t>費用内訳テーブル (nullなら「土地あり」)</t>
         </is>
       </c>
     </row>
@@ -3343,20 +4638,18 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>3391 (建物+土地+諸費用)</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>totalPrice</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー最上部の大きな数字
-費用内訳テーブル「総額」
-一覧カードの価格表示</t>
+          <t>ヒーロー最上部の大きな数字 / 費用内訳「総額」/ カード価格</t>
         </is>
       </c>
     </row>
@@ -3377,16 +4670,42 @@
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>familyStructure</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>ヒーロー「夫婦 + 子ども1人」
-物件情報テーブル「家族構成」
-施主コメント末尾の署名</t>
+          <t>ヒーロー / 物件情報 / 施主コメント署名</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>キャッチコピー</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>「家族の暮らしに寄り添う28坪の平屋」</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>catchphrase</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>パンくず下のサブタイトル</t>
         </is>
       </c>
     </row>
@@ -3398,23 +4717,23 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>キャッチコピー (1行)</t>
+          <t>事例の説明 (200-300文字)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>「家族の暮らしに寄り添う、28坪の3LDK平屋」</t>
+          <t>○○が手掛けた28坪の3LDK。…</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>catchphrase</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>パンくず下のサブタイトル</t>
+          <t>ヒーローの説明文</t>
         </is>
       </c>
     </row>
@@ -3426,23 +4745,23 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>事例の説明 (200〜300文字)</t>
+          <t>設計のポイント①</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>「○○が手掛けた28坪の3LDK。…ぺいほーむ注目の完成事例です。」</t>
+          <t>回遊動線で家事効率を最大化</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>description</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>designPoints[0]</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>ヒーローの説明文 (タイトル下)</t>
+          <t>「設計のポイント」カード①</t>
         </is>
       </c>
     </row>
@@ -3454,23 +4773,23 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>設計のポイント①</t>
+          <t>設計のポイント②</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>「回遊動線で家事効率を最大化」等</t>
+          <t>高断熱サッシで光と断熱を両立</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>designPoints[0]</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>designPoints[1]</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>「設計のポイント」セクション カード①</t>
+          <t>同上 カード②</t>
         </is>
       </c>
     </row>
@@ -3482,23 +4801,23 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>設計のポイント②</t>
+          <t>設計のポイント③</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>「高断熱サッシで光を取り込みながら断熱」</t>
+          <t>シューズクローク→パントリー直結動線</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>designPoints[1]</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>designPoints[2]</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>「設計のポイント」セクション カード②</t>
+          <t>同上 カード③</t>
         </is>
       </c>
     </row>
@@ -3510,23 +4829,23 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>設計のポイント③</t>
+          <t>施主コメント (100-200文字)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>「シューズクロークからパントリーへの直結動線」</t>
+          <t>初めての家づくりで不安でしたが…</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>designPoints[2]</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>ownerComment</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>「設計のポイント」セクション カード③</t>
+          <t>「施主様の声」セクション (引用)</t>
         </is>
       </c>
     </row>
@@ -3538,628 +4857,663 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>施主コメント (100〜200文字)</t>
+          <t>特徴タグ (カンマ区切り)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>「初めての家づくりで不安でしたが…」</t>
+          <t>平屋, 高性能, 回遊動線, 中庭, ZEH</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>ownerComment</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>tags</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>「施主様の声」セクション (引用表示)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>特徴タグ (複数、カンマ区切り)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>平屋, 高性能, 回遊動線, 中庭, ZEH</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>tags</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>「特徴タグ」セクション (#タグ表示)
-一覧のタグフィルター</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>■ 写真データ（photos フィールド — 外観8枚 + 内観12枚 = 20枚）</t>
+          <t>「特徴タグ」セクション / フィルター</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>■ 写真データ (photos[] — 外観8枚 + 内観12枚 = 20枚)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>外観①</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>外観 正面 (メインビジュアル)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>建物全体が入る正面</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>photos[0] exterior</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>写真ギャラリー「外観」タブ メイン</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観②</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>外観 正面 (メインビジュアル)</t>
+          <t>外観 全体 (斜め)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>建物全体が入る正面アングル</t>
+          <t>立体感がわかる角度</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>photos[0] exterior</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>photos[1] exterior</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ
-メイン画像 (デフォルト表示)</t>
+          <t>写真ギャラリー「外観」タブ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観③</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>外観 全体 (斜めアングル)</t>
+          <t>外観 玄関アプローチ</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>建物の立体感がわかる角度</t>
+          <t>門扉〜玄関ドア</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>photos[1] exterior</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>photos[2] exterior</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観④</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>外観 玄関アプローチ</t>
+          <t>外観 庭側</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>門扉〜玄関ドアまでの動線</t>
+          <t>ウッドデッキ・庭</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>photos[2] exterior</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>photos[3] exterior</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観⑤</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>外観 庭側</t>
+          <t>外観 夕景</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>ウッドデッキ・庭・テラスが見える角度</t>
+          <t>照明が映える夕方</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>photos[3] exterior</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>photos[4] exterior</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観⑥</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>外観 夕景</t>
+          <t>外観 駐車場側</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>照明が映える夕方〜夜の外観 (撮影可能なら)</t>
+          <t>カーポート</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>photos[4] exterior</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>photos[5] exterior</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観⑦</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>外観 駐車場側</t>
+          <t>外観 屋根</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>カーポート・駐車スペースが見える角度</t>
+          <t>屋根形状・太陽光</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>photos[5] exterior</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>photos[6] exterior</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>外観⑧</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>外観 屋根</t>
+          <t>外観 植栽・外構</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>屋根形状・太陽光パネルが見える角度</t>
+          <t>庭・フェンス</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>photos[6] exterior</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>photos[7] exterior</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>外観写真</t>
+          <t>内観①</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>外観 植栽・外構</t>
+          <t>LDK 全体</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>庭の植栽・フェンス・アプローチ</t>
+          <t>リビング・ダイニング・キッチン一望</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>photos[7] exterior</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>photos[8] interior</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「外観」タブ</t>
+          <t>写真ギャラリー「内観」タブ メイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>内観②</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>正面 (設備・収納)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>photos[9] interior</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観③</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>LDK 全体</t>
+          <t>ダイニング</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>リビング・ダイニング・キッチンが一望できるアングル</t>
+          <t>食卓・窓からの採光</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>photos[8] interior</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>photos[10] interior</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ
-メイン画像 (内観選択時)</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観④</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>キッチン</t>
+          <t>リビング</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>キッチン正面 (設備・収納が見える角度)</t>
+          <t>ソファ方向の眺め</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>photos[9] interior</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>photos[11] interior</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑤</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ダイニング</t>
+          <t>主寝室</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>食卓スペース・窓からの採光</t>
+          <t>ベッド配置・WIC入口</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>photos[10] interior</t>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>photos[12] interior</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑥</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>リビング</t>
+          <t>洋室</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>ソファ方向からの眺め・テレビ壁面</t>
+          <t>広さ・窓・収納</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>photos[11] interior</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>photos[13] interior</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑦</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>主寝室</t>
+          <t>WIC・収納</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>ベッド配置・WIC入口が見える角度</t>
+          <t>ウォークインクローゼット</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>photos[12] interior</t>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>photos[14] interior</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑧</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>洋室 (子ども部屋等)</t>
+          <t>洗面脱衣室</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>広さ・窓・収納がわかるアングル</t>
+          <t>洗面台・鏡</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>photos[13] interior</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>photos[15] interior</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑨</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>WIC・収納</t>
+          <t>浴室</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>ウォークインクローゼット or 大型収納</t>
+          <t>浴槽・シャワー</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>photos[14] interior</t>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>photos[16] interior</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑩</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>洗面脱衣室</t>
+          <t>トイレ</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>洗面台・鏡・収納</t>
+          <t>便器・アクセントクロス</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>photos[15] interior</t>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>photos[17] interior</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑪</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>浴室</t>
+          <t>玄関ホール</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>浴槽・シャワー・窓</t>
+          <t>ドアを開けた第一印象</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>photos[16] interior</t>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>photos[18] interior</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>内観写真</t>
+          <t>内観⑫</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>トイレ</t>
+          <t>ウッドデッキ/テラス</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>便器・手洗い・アクセントクロス</t>
+          <t>屋外リビング</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>photos[17] interior</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>photos[19] interior</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>写真ギャラリー「内観」タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>内観写真</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>玄関ホール</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>玄関ドアを開けた時の第一印象</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>photos[18] interior</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>写真ギャラリー「内観」タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>内観写真</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>ウッドデッキ/テラス</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>屋外リビング・BBQスペース</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>photos[19] interior</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>写真ギャラリー「内観」タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>■ 間取り図（会員限定セクション）</t>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>■ 間取り図 (会員限定セクション)</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>間取り図データの提供形式</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>PDF / CAD / 紙 / なし</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>「間取り図」セクション (会員限定フル表示 / 非会員ブラー+登録CTA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>間取り図</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>間取り図の掲載許可</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>許可 / 不可</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>セクション表示判定</t>
         </is>
       </c>
     </row>
@@ -4171,25 +5525,23 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>間取り図データの提供形式</t>
+          <t>各部屋の面積</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>PDF / CAD / 紙 / なし</t>
+          <t>LDK 37㎡ / 主寝室 14㎡ 等</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>「間取り図」セクション
-(会員のみフル表示
-非会員はブラー+登録CTA)</t>
+          <t>SVG間取り図の面積ラベル</t>
         </is>
       </c>
     </row>
@@ -4201,86 +5553,91 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>間取り図の掲載許可</t>
+          <t>特記事項</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>許可 / 不可</t>
+          <t>ロフト / 小上がり和室 等</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>間取り図セクション表示判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>間取り図</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>各部屋の面積 (わかれば)</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>LDK 37㎡ / 主寝室 14㎡ / 洋室 8㎡ 等</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="8" t="inlineStr">
+          <t>SVG内の注記</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>■ 撮影・掲載条件</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能日程 (候補3日程)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>5/10, 5/15, 5/20</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>SVG 間取り図の面積ラベル</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>間取り図</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>特記事項 (スキップフロア等)</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>ロフトあり / 小上がり和室 等</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>撮影条件</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>撮影可能時間帯</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>10:00〜16:00</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>間取り図の注記</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>■ 撮影・掲載条件（コードには直接反映しないが運用に必要）</t>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール管理</t>
         </is>
       </c>
     </row>
@@ -4292,23 +5649,23 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>撮影可能な日程 (候補 3 日程)</t>
+          <t>駐車場の有無</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>5/10, 5/15, 5/20</t>
+          <t>あり/なし</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>スケジュール管理</t>
+          <t>ロケハン</t>
         </is>
       </c>
     </row>
@@ -4320,23 +5677,23 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>撮影可能な時間帯</t>
+          <t>鍵の受け渡し方法</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10:00〜16:00</t>
+          <t>工務店開錠/施主在宅</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>スケジュール管理</t>
+          <t>事前準備</t>
         </is>
       </c>
     </row>
@@ -4348,23 +5705,23 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>駐車場の有無 (撮影車両)</t>
+          <t>家具配置状態</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>あり (2台分) / なし</t>
+          <t>入居前(空室)/入居後(家具あり)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>ロケハン</t>
+          <t>写真の雰囲気</t>
         </is>
       </c>
     </row>
@@ -4376,16 +5733,16 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>鍵の受け渡し方法 (OB宅の場合)</t>
+          <t>セッティング</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>工務店が開錠 / 施主在宅</t>
+          <t>工務店準備/ぺいほーむ持参/なし</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4404,79 +5761,107 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>家具・家電の配置状態</t>
+          <t>撮影NG場所</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>入居前 (空室) / 入居後 (家具あり)</t>
+          <t>隣家/私物/住所表示</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>写真の雰囲気決定</t>
+          <t>カメラマン指示</t>
         </is>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>撮影条件</t>
+          <t>掲載条件</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>インテリア小物のセッティング</t>
+          <t>サイト掲載許可</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>工務店が準備 / ぺいほーむが持参 / なし</t>
+          <t>許可/不可</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>事前準備</t>
+          <t>掲載判断</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>撮影条件</t>
+          <t>掲載条件</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>撮影 NG の場所</t>
+          <t>価格公開範囲</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>隣家の窓 / 施主の私物 / 住所表示</t>
+          <t>全公開/本体のみ/非公開</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>カメラマン指示</t>
+          <t>費用内訳セクション表示制御</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>掲載条件</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>施主顔写真掲載可否</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>可/不可</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>施主コメントセクション</t>
         </is>
       </c>
     </row>
@@ -4488,23 +5873,23 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>ぺいほーむ /case-studies への掲載許可</t>
+          <t>プレビュー確認希望</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>許可 / 不可</t>
+          <t>あり/なし</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>掲載判断</t>
+          <t>公開フロー</t>
         </is>
       </c>
     </row>
@@ -4516,23 +5901,23 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>価格情報の公開範囲</t>
+          <t>SNS使用許可</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>全公開 / 本体のみ / 非公開</t>
+          <t>全許可/一部/不可</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>費用内訳セクションの表示制御</t>
+          <t>SNS運用</t>
         </is>
       </c>
     </row>
@@ -4544,105 +5929,21 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>施主の顔写真掲載可否</t>
+          <t>修正・削除依頼の窓口</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>可 / 不可</t>
+          <t>工務店担当○○/メール</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>施主コメントセクション</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>掲載前プレビュー確認の希望</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>あり / なし</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>公開フロー</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>SNS 写真使用許可 (X/Instagram/Threads)</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>全許可 / 一部 / 不可</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>SNS 運用</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>掲載条件</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>掲載後の修正・削除依頼の窓口</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>工務店担当○○ / メール / 電話</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>運用</t>
         </is>
@@ -4651,11 +5952,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A55:F55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4667,7 +5968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4688,7 +5989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>撮影完了後の編集→レビュー→公開→掲載の確認項目</t>
+          <t>撮影→編集→レビュー→公開→掲載</t>
         </is>
       </c>
     </row>
@@ -4720,7 +6021,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>完了 ✓</t>
+          <t>完了✓</t>
         </is>
       </c>
     </row>
@@ -4735,7 +6036,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>撮影データ (RAW/動画) のバックアップ完了</t>
+          <t>撮影データバックアップ完了</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -4761,7 +6062,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>撮影データの受け渡し完了</t>
+          <t>撮影データ受け渡し完了</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4787,7 +6088,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>動画編集完了 (カット/テロップ/ナレーション)</t>
+          <t>動画編集完了</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4839,7 +6140,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>写真セレクト (外観8枚+内観12枚=20枚)</t>
+          <t>写真セレクト(外観8+内観12=20枚)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4865,7 +6166,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>写真レタッチ完了 (明るさ/色調/水平)</t>
+          <t>写真レタッチ完了</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4886,22 +6187,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>編集(写真)</t>
+          <t>レビュー</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>写真リサイズ (Web用800x600+高解像度)</t>
+          <t>工務店による確認OK</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>編集者</t>
+          <t>営業</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>撮影後5日</t>
+          <t>公開3日前</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -4917,7 +6218,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>工務店による動画プレビュー確認OK</t>
+          <t>施主による確認OK</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4938,22 +6239,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>工務店による写真確認OK</t>
+          <t>YouTubeアップロード完了</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>掲載3日前</t>
+          <t>公開日</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -4964,22 +6265,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>施主による確認OK (必要な場合)</t>
+          <t>videos-data.tsにエントリ追加</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>営業</t>
+          <t>エンジニア</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>公開3日前</t>
+          <t>公開日</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -4990,22 +6291,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>レビュー</t>
+          <t>公開(動画)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>NG箇所の修正完了</t>
+          <t>properties.tsにエントリ追加(価格/設備/性能/間取り等)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>編集者</t>
+          <t>エンジニア</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>公開1日前</t>
+          <t>公開日</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -5016,12 +6317,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>公開(動画)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>YouTube アップロード完了</t>
+          <t>ヒアリングシート⑤の全回答をデータ化</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -5031,7 +6332,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>公開日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -5042,22 +6343,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>公開(動画)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>YouTube タイトル・説明文・タグ設定</t>
+          <t>case-studies-data.tsにエントリ追加</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>エンジニア</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>公開日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -5068,12 +6369,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>公開(動画)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>videos-data.ts に新規エントリ追加</t>
+          <t>写真20枚をSupabase Storageにアップロード</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -5083,7 +6384,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>公開日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -5094,22 +6395,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>公開(動画)</t>
+          <t>掲載(事例)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>/videos で表示確認 (PC+モバイル)</t>
+          <t>間取り図データの登録(会員限定)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>エンジニア</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>公開日</t>
+          <t>掲載日</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -5125,7 +6426,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>ヒアリングシート⑤の全回答をデータ化</t>
+          <t>/case-studies/[id]で全セクション表示確認</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -5146,22 +6447,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>掲載(事例)</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>case-studies-data.ts に新規エントリ追加</t>
+          <t>X/Instagram/Threadsでの告知</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>エンジニア</t>
+          <t>代表</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>掲載日</t>
+          <t>掲載翌日</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -5172,181 +6473,25 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>掲載(事例)</t>
+          <t>請求</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>写真20枚を Supabase Storage にアップロード</t>
+          <t>撮影費¥150,000の請求書発行(Phase2〜)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>エンジニア</t>
+          <t>経理</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>掲載日</t>
+          <t>撮影月末</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>掲載(事例)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>間取り図データの登録 (会員限定)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>エンジニア</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>掲載日</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>掲載(事例)</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>/case-studies/[id] で全セクション表示確認</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>掲載日</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>掲載(事例)</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>写真ギャラリー 外観/内観タブ動作確認</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>掲載日</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>掲載(事例)</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>間取り図 会員/非会員の表示切替確認</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>掲載日</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>SNS</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>X/Instagram/Threads での告知投稿</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>代表</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>掲載翌日</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>請求</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>撮影費 ¥150,000 の請求書発行 (Phase 2〜)</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>経理</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>撮影月末</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
